--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BUCHA BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BUCHA BENGALA.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUCHA BENG VEDAMOTOS CROSSER XTZ125 2003 A 2016</t>
+          <t>BUCHA BENGALA VEDAMOTOS CROSSER XTZ125 2003 A 2016</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BUCHA BENG VEDAMOTOS TORNADO XR250 2002 A 2008/ XRE300</t>
+          <t>BUCHA BENGALA VEDAMOTOS TORNADO XR250 2002 A 2008/ XRE300</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUCHA BENG VEDAMOTOS LANDER XTZ250 2007 A 2015</t>
+          <t>BUCHA BENGALA VEDAMOTOS LANDER XTZ250 2007 A 2015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BUCHA BENG SMARTFOX XRE300 TORNADO XR250 FALCON400 2008/ CB600 2010</t>
+          <t>BUCHA BENGALA SMARTFOX XRE300/ TORNADO XR250/ FALCON400 2008/ CB600 2010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +532,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BUCHA BENG (PAR) MOTOBOR+ FAN CG TITAN150-160/ BROS NXR125-150-160</t>
+          <t>BUCHA BENGALA (PAR) MOTOPOR+ FAN CG TITAN150-160/ BROS NXR125-150-160</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -541,7 +557,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,7 +574,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUCHA BENG SMARTFOX XR250 TORNADO</t>
+          <t>BUCHA BENGALA SMARTFOX XR250 TORNADO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -579,7 +599,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BUCHA BENG SMARTFOX FALCON400/ CB600</t>
+          <t>BUCHA BENGALA SMARTFOX FALCON400/ CB600</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -587,7 +607,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +620,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUCHA BENG IRON CG TITAN150-160/ BROS NXR125 197587</t>
+          <t>BUCHA BENGALA IRON CG TITAN150-160/ BROS NXR125 197587</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -604,7 +628,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -617,7 +645,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUCHA BENG TRILHA TITAN150 2004 A 2015/ BROS NXR150 2003 A 2014/ NXR160 2015 A 2022/ XRE190 2015 A 2016</t>
+          <t>BUCHA BENGALA TRILHA TITAN150 2004 A 2015/ BROS NXR150 2003 A 2014/ NXR160 2015 A 2022/ XRE190 2015 A 2016</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -625,7 +653,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +670,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUCHA BENG IRON CB300R 2009 A 2015/ CB500 1997 A 2005/ CRF250F 2007 A 2019 197586</t>
+          <t>BUCHA BENGALA IRON CB300R 2009 A 2015/ CB500 1997 A 2005/ CRF250F 2007 A 2019 197586</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BUCHA BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BUCHA BENGALA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -628,11 +588,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -653,11 +608,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -676,11 +626,6 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
